--- a/evaluasi_skipgram_naive_bayes.xlsx
+++ b/evaluasi_skipgram_naive_bayes.xlsx
@@ -491,7 +491,7 @@
         <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
         <v>0.925</v>

--- a/evaluasi_skipgram_naive_bayes.xlsx
+++ b/evaluasi_skipgram_naive_bayes.xlsx
@@ -494,16 +494,16 @@
         <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>0.925</v>
+        <v>0.95</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9347826086956521</v>
+        <v>0.9545454545454546</v>
       </c>
       <c r="H2" t="n">
-        <v>0.925</v>
+        <v>0.95</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9245757385292269</v>
+        <v>0.949874686716792</v>
       </c>
     </row>
   </sheetData>
